--- a/input/Ejemplos Input/vacio_factura_c.xlsx
+++ b/input/Ejemplos Input/vacio_factura_c.xlsx
@@ -1,159 +1,56 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Factura C" sheetId="1" r:id="rId1"/>
-    <sheet name="Nota Credito C" sheetId="2" r:id="rId2"/>
-    <sheet name="Nota Debito C" sheetId="3" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Factura C" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nota Credito C" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nota Debito C" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="33">
-  <si>
-    <t>Tipo Dato</t>
-  </si>
-  <si>
-    <t>Fecha</t>
-  </si>
-  <si>
-    <t>Periodo Desde</t>
-  </si>
-  <si>
-    <t>Periodo Hasta</t>
-  </si>
-  <si>
-    <t>Condicion frente al IVA</t>
-  </si>
-  <si>
-    <t>Tipo Doc</t>
-  </si>
-  <si>
-    <t>Cliente</t>
-  </si>
-  <si>
-    <t>Documento</t>
-  </si>
-  <si>
-    <t>Domicilio</t>
-  </si>
-  <si>
-    <t>Cant.</t>
-  </si>
-  <si>
-    <t>Descripcion</t>
-  </si>
-  <si>
-    <t>$ Unit.</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Condición Venta</t>
-  </si>
-  <si>
-    <t>Unidad Medida</t>
-  </si>
-  <si>
-    <t>% Bonificación</t>
-  </si>
-  <si>
-    <t>Importe Bonificación</t>
-  </si>
-  <si>
-    <t>Importe Op Ex</t>
-  </si>
-  <si>
-    <t>Importe IVA</t>
-  </si>
-  <si>
-    <t>Importe Tributos</t>
-  </si>
-  <si>
-    <t>Concepto</t>
-  </si>
-  <si>
-    <t>Codigo Otros Tributos</t>
-  </si>
-  <si>
-    <t>Descripión Otros Tributos</t>
-  </si>
-  <si>
-    <t>Base Imponible Otros Tributos</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Comprobación</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> CAE</t>
-  </si>
-  <si>
-    <t>Fecha Vencimiento CAE</t>
-  </si>
-  <si>
-    <t>Número Comprobante</t>
-  </si>
-  <si>
-    <t>Tipo</t>
-  </si>
-  <si>
-    <t>Importe Total</t>
-  </si>
-  <si>
-    <t>Motivo Nota</t>
-  </si>
-  <si>
-    <t>Número Comprobante Original</t>
-  </si>
-  <si>
-    <t>Observaciones</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -170,7 +67,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <fgColor theme="0" tint="-0.1499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -353,92 +250,154 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="7"/>
   </cellStyleXfs>
   <cellXfs count="30">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Buena" xfId="1" builtinId="26"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -726,185 +685,283 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:AG14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="15.7109375" style="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.28515625" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.7109375" style="14" customWidth="1"/>
-    <col min="6" max="7" width="15.7109375" style="14" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" style="16" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.7109375" style="14" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.7109375" style="16" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="14" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="15.7109375" style="16" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.7109375" style="14" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.5703125" style="14" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.7109375" style="17" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="21.28515625" style="17" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="15.7109375" style="19" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.7109375" style="19" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="19.5703125" style="19" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.7109375" style="16" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="25.85546875" style="14" customWidth="1"/>
-    <col min="24" max="24" width="32.140625" style="14" customWidth="1"/>
-    <col min="25" max="25" width="31.140625" style="14" customWidth="1"/>
-    <col min="30" max="30" width="17.7109375" style="19" customWidth="1"/>
-    <col min="31" max="31" width="15.140625" style="19" customWidth="1"/>
-    <col min="32" max="32" width="26.28515625" style="19" customWidth="1"/>
-    <col min="33" max="33" width="22.28515625" style="19" customWidth="1"/>
+    <col width="15.7109375" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
+    <col width="15.7109375" bestFit="1" customWidth="1" style="15" min="2" max="3"/>
+    <col width="22.28515625" bestFit="1" customWidth="1" style="15" min="4" max="4"/>
+    <col width="22.7109375" customWidth="1" style="14" min="5" max="5"/>
+    <col width="15.7109375" bestFit="1" customWidth="1" style="14" min="6" max="7"/>
+    <col width="15.7109375" bestFit="1" customWidth="1" style="16" min="8" max="8"/>
+    <col width="15.7109375" bestFit="1" customWidth="1" style="14" min="9" max="9"/>
+    <col width="15.7109375" bestFit="1" customWidth="1" style="16" min="10" max="10"/>
+    <col width="15.7109375" bestFit="1" customWidth="1" style="14" min="11" max="11"/>
+    <col width="15.7109375" bestFit="1" customWidth="1" style="16" min="12" max="13"/>
+    <col width="15.7109375" bestFit="1" customWidth="1" style="14" min="14" max="14"/>
+    <col width="13.5703125" bestFit="1" customWidth="1" style="14" min="15" max="15"/>
+    <col width="15.7109375" bestFit="1" customWidth="1" style="17" min="16" max="16"/>
+    <col width="21.28515625" bestFit="1" customWidth="1" style="17" min="17" max="17"/>
+    <col width="15.7109375" bestFit="1" customWidth="1" style="19" min="18" max="19"/>
+    <col width="16.7109375" bestFit="1" customWidth="1" style="19" min="20" max="20"/>
+    <col width="19.5703125" bestFit="1" customWidth="1" style="19" min="21" max="21"/>
+    <col width="15.7109375" bestFit="1" customWidth="1" style="16" min="22" max="22"/>
+    <col width="25.85546875" customWidth="1" style="14" min="23" max="23"/>
+    <col width="32.140625" customWidth="1" style="14" min="24" max="24"/>
+    <col width="31.140625" customWidth="1" style="14" min="25" max="25"/>
+    <col width="17.7109375" customWidth="1" style="19" min="30" max="30"/>
+    <col width="15.140625" customWidth="1" style="19" min="31" max="31"/>
+    <col width="26.28515625" customWidth="1" style="19" min="32" max="32"/>
+    <col width="22.28515625" customWidth="1" style="19" min="33" max="33"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="V1" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="W1" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="X1" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y1" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="AD1" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="AE1" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF1" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="AG1" s="18" t="s">
-        <v>27</v>
+    <row r="1" ht="19.5" customHeight="1" s="14" thickBot="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Tipo Dato</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Periodo Desde</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Periodo Hasta</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Condicion frente al IVA</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Tipo Doc</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>Documento</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>Domicilio</t>
+        </is>
+      </c>
+      <c r="J1" s="8" t="inlineStr">
+        <is>
+          <t>Cant.</t>
+        </is>
+      </c>
+      <c r="K1" s="6" t="inlineStr">
+        <is>
+          <t>Descripcion</t>
+        </is>
+      </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>$ Unit.</t>
+        </is>
+      </c>
+      <c r="M1" s="10" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="N1" s="11" t="inlineStr">
+        <is>
+          <t>Condición Venta</t>
+        </is>
+      </c>
+      <c r="O1" s="11" t="inlineStr">
+        <is>
+          <t>Unidad Medida</t>
+        </is>
+      </c>
+      <c r="P1" s="12" t="inlineStr">
+        <is>
+          <t>% Bonificación</t>
+        </is>
+      </c>
+      <c r="Q1" s="12" t="inlineStr">
+        <is>
+          <t>Importe Bonificación</t>
+        </is>
+      </c>
+      <c r="R1" s="13" t="inlineStr">
+        <is>
+          <t>Importe Op Ex</t>
+        </is>
+      </c>
+      <c r="S1" s="13" t="inlineStr">
+        <is>
+          <t>Importe IVA</t>
+        </is>
+      </c>
+      <c r="T1" s="13" t="inlineStr">
+        <is>
+          <t>Importe Tributos</t>
+        </is>
+      </c>
+      <c r="U1" s="13" t="inlineStr">
+        <is>
+          <t>Observaciones</t>
+        </is>
+      </c>
+      <c r="V1" s="10" t="inlineStr">
+        <is>
+          <t>Concepto</t>
+        </is>
+      </c>
+      <c r="W1" s="10" t="inlineStr">
+        <is>
+          <t>Codigo Otros Tributos</t>
+        </is>
+      </c>
+      <c r="X1" s="10" t="inlineStr">
+        <is>
+          <t>Descripión Otros Tributos</t>
+        </is>
+      </c>
+      <c r="Y1" s="10" t="inlineStr">
+        <is>
+          <t>Base Imponible Otros Tributos</t>
+        </is>
+      </c>
+      <c r="AD1" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Comprobación</t>
+        </is>
+      </c>
+      <c r="AE1" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CAE</t>
+        </is>
+      </c>
+      <c r="AF1" s="18" t="inlineStr">
+        <is>
+          <t>Fecha Vencimiento CAE</t>
+        </is>
+      </c>
+      <c r="AG1" s="18" t="inlineStr">
+        <is>
+          <t>Número Comprobante</t>
+        </is>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="W14" s="29"/>
+    <row r="14">
+      <c r="W14" s="29" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.140625" style="19" customWidth="1"/>
-    <col min="2" max="2" width="34.85546875" style="28" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" style="15" customWidth="1"/>
-    <col min="4" max="4" width="22.140625" style="19" customWidth="1"/>
-    <col min="5" max="5" width="26.5703125" style="19" customWidth="1"/>
-    <col min="6" max="6" width="23.7109375" style="16" customWidth="1"/>
-    <col min="7" max="7" width="25.85546875" style="19" customWidth="1"/>
-    <col min="8" max="8" width="30.140625" style="16" customWidth="1"/>
-    <col min="9" max="9" width="24.140625" style="16" customWidth="1"/>
-    <col min="10" max="10" width="38" style="19" customWidth="1"/>
+    <col width="22.140625" customWidth="1" style="19" min="1" max="1"/>
+    <col width="34.85546875" customWidth="1" style="28" min="2" max="2"/>
+    <col width="22.85546875" customWidth="1" style="15" min="3" max="3"/>
+    <col width="22.85546875" customWidth="1" style="19" min="4" max="4"/>
+    <col width="22.85546875" customWidth="1" style="19" min="5" max="5"/>
+    <col width="26" customWidth="1" style="16" min="6" max="6"/>
+    <col width="25.85546875" customWidth="1" style="19" min="7" max="7"/>
+    <col width="30.140625" customWidth="1" style="16" min="8" max="8"/>
+    <col width="24.140625" customWidth="1" style="16" min="9" max="9"/>
+    <col width="38" customWidth="1" style="19" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="I1" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="J1" s="25" t="s">
-        <v>30</v>
+    <row r="1" ht="15.75" customHeight="1" s="14" thickBot="1">
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B1" s="27" t="inlineStr">
+        <is>
+          <t>Número Comprobante Original</t>
+        </is>
+      </c>
+      <c r="C1" s="20" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="D1" s="20" t="inlineStr">
+        <is>
+          <t>Periodo Desde</t>
+        </is>
+      </c>
+      <c r="E1" s="20" t="inlineStr">
+        <is>
+          <t>Periodo Hasta</t>
+        </is>
+      </c>
+      <c r="F1" s="20" t="inlineStr">
+        <is>
+          <t>Fecha vencimiento pago</t>
+        </is>
+      </c>
+      <c r="G1" s="21" t="inlineStr">
+        <is>
+          <t>Tipo Doc</t>
+        </is>
+      </c>
+      <c r="H1" s="22" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="I1" s="23" t="inlineStr">
+        <is>
+          <t>Documento</t>
+        </is>
+      </c>
+      <c r="J1" s="21" t="inlineStr">
+        <is>
+          <t>Domicilio</t>
+        </is>
+      </c>
+      <c r="K1" s="24" t="inlineStr">
+        <is>
+          <t>Importe Total</t>
+        </is>
+      </c>
+      <c r="L1" s="24" t="inlineStr">
+        <is>
+          <t>Concepto</t>
+        </is>
+      </c>
+      <c r="M1" s="25" t="inlineStr">
+        <is>
+          <t>Motivo Nota</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -913,53 +970,92 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.140625" style="19" customWidth="1"/>
-    <col min="2" max="2" width="34.85546875" style="28" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" style="15" customWidth="1"/>
-    <col min="4" max="4" width="22.140625" style="19" customWidth="1"/>
-    <col min="5" max="5" width="26.5703125" style="19" customWidth="1"/>
-    <col min="6" max="6" width="23.7109375" style="16" customWidth="1"/>
-    <col min="7" max="7" width="25.85546875" style="19" customWidth="1"/>
-    <col min="8" max="8" width="30.140625" style="16" customWidth="1"/>
-    <col min="9" max="9" width="24.140625" style="16" customWidth="1"/>
-    <col min="10" max="10" width="38" style="19" customWidth="1"/>
-    <col min="11" max="16384" width="11.42578125" style="14"/>
+    <col width="22.140625" customWidth="1" style="19" min="1" max="1"/>
+    <col width="34.85546875" customWidth="1" style="28" min="2" max="2"/>
+    <col width="22.85546875" customWidth="1" style="15" min="3" max="3"/>
+    <col width="22.85546875" customWidth="1" style="19" min="4" max="4"/>
+    <col width="22.85546875" customWidth="1" style="19" min="5" max="5"/>
+    <col width="26" customWidth="1" style="16" min="6" max="6"/>
+    <col width="25.85546875" customWidth="1" style="19" min="7" max="7"/>
+    <col width="30.140625" customWidth="1" style="16" min="8" max="8"/>
+    <col width="24.140625" customWidth="1" style="16" min="9" max="9"/>
+    <col width="38" customWidth="1" style="19" min="10" max="10"/>
+    <col width="11.42578125" customWidth="1" style="14" min="11" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="27" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="I1" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="J1" s="25" t="s">
-        <v>30</v>
+    <row r="1" ht="15" customHeight="1" s="14" thickBot="1">
+      <c r="A1" s="26" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="B1" s="27" t="inlineStr">
+        <is>
+          <t>Número Comprobante Original</t>
+        </is>
+      </c>
+      <c r="C1" s="20" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="D1" s="20" t="inlineStr">
+        <is>
+          <t>Periodo Desde</t>
+        </is>
+      </c>
+      <c r="E1" s="20" t="inlineStr">
+        <is>
+          <t>Periodo Hasta</t>
+        </is>
+      </c>
+      <c r="F1" s="20" t="inlineStr">
+        <is>
+          <t>Fecha vencimiento pago</t>
+        </is>
+      </c>
+      <c r="G1" s="21" t="inlineStr">
+        <is>
+          <t>Tipo Doc</t>
+        </is>
+      </c>
+      <c r="H1" s="22" t="inlineStr">
+        <is>
+          <t>Cliente</t>
+        </is>
+      </c>
+      <c r="I1" s="23" t="inlineStr">
+        <is>
+          <t>Documento</t>
+        </is>
+      </c>
+      <c r="J1" s="21" t="inlineStr">
+        <is>
+          <t>Domicilio</t>
+        </is>
+      </c>
+      <c r="K1" s="24" t="inlineStr">
+        <is>
+          <t>Importe Total</t>
+        </is>
+      </c>
+      <c r="L1" s="24" t="inlineStr">
+        <is>
+          <t>Concepto</t>
+        </is>
+      </c>
+      <c r="M1" s="25" t="inlineStr">
+        <is>
+          <t>Motivo Nota</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/input/Ejemplos Input/vacio_factura_c.xlsx
+++ b/input/Ejemplos Input/vacio_factura_c.xlsx
@@ -1,56 +1,168 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\InvoicePRO\invoice-pro-back-local\input\Ejemplos Input\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F6C7C12-A794-40A0-93FD-D9E6AF0B29C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="2895" yWindow="2895" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Factura C" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nota Credito C" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nota Debito C" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Factura C" sheetId="1" r:id="rId1"/>
+    <sheet name="Nota Credito C" sheetId="2" r:id="rId2"/>
+    <sheet name="Nota Debito C" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="34">
+  <si>
+    <t>Tipo Dato</t>
+  </si>
+  <si>
+    <t>Fecha</t>
+  </si>
+  <si>
+    <t>Periodo Desde</t>
+  </si>
+  <si>
+    <t>Periodo Hasta</t>
+  </si>
+  <si>
+    <t>Condicion frente al IVA</t>
+  </si>
+  <si>
+    <t>Tipo Doc</t>
+  </si>
+  <si>
+    <t>Cliente</t>
+  </si>
+  <si>
+    <t>Documento</t>
+  </si>
+  <si>
+    <t>Domicilio</t>
+  </si>
+  <si>
+    <t>Cant.</t>
+  </si>
+  <si>
+    <t>Descripcion</t>
+  </si>
+  <si>
+    <t>$ Unit.</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Condición Venta</t>
+  </si>
+  <si>
+    <t>Unidad Medida</t>
+  </si>
+  <si>
+    <t>% Bonificación</t>
+  </si>
+  <si>
+    <t>Importe Bonificación</t>
+  </si>
+  <si>
+    <t>Importe Op Ex</t>
+  </si>
+  <si>
+    <t>Importe IVA</t>
+  </si>
+  <si>
+    <t>Importe Tributos</t>
+  </si>
+  <si>
+    <t>Observaciones</t>
+  </si>
+  <si>
+    <t>Concepto</t>
+  </si>
+  <si>
+    <t>Codigo Otros Tributos</t>
+  </si>
+  <si>
+    <t>Descripión Otros Tributos</t>
+  </si>
+  <si>
+    <t>Base Imponible Otros Tributos</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Comprobación</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CAE</t>
+  </si>
+  <si>
+    <t>Fecha Vencimiento CAE</t>
+  </si>
+  <si>
+    <t>Número Comprobante</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Número Comprobante Original</t>
+  </si>
+  <si>
+    <t>Fecha vencimiento pago</t>
+  </si>
+  <si>
+    <t>Importe Total</t>
+  </si>
+  <si>
+    <t>Motivo Nota</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <u val="single"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -67,7 +179,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.1499984740745262"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -249,155 +361,97 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="7"/>
   </cellStyleXfs>
-  <cellXfs count="30">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="31">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Buena" xfId="1" builtinId="26"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -685,283 +739,198 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <dimension ref="A1:AH14"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="15.7109375" bestFit="1" customWidth="1" style="14" min="1" max="1"/>
-    <col width="15.7109375" bestFit="1" customWidth="1" style="15" min="2" max="3"/>
-    <col width="22.28515625" bestFit="1" customWidth="1" style="15" min="4" max="4"/>
-    <col width="22.7109375" customWidth="1" style="14" min="5" max="5"/>
-    <col width="15.7109375" bestFit="1" customWidth="1" style="14" min="6" max="7"/>
-    <col width="15.7109375" bestFit="1" customWidth="1" style="16" min="8" max="8"/>
-    <col width="15.7109375" bestFit="1" customWidth="1" style="14" min="9" max="9"/>
-    <col width="15.7109375" bestFit="1" customWidth="1" style="16" min="10" max="10"/>
-    <col width="15.7109375" bestFit="1" customWidth="1" style="14" min="11" max="11"/>
-    <col width="15.7109375" bestFit="1" customWidth="1" style="16" min="12" max="13"/>
-    <col width="15.7109375" bestFit="1" customWidth="1" style="14" min="14" max="14"/>
-    <col width="13.5703125" bestFit="1" customWidth="1" style="14" min="15" max="15"/>
-    <col width="15.7109375" bestFit="1" customWidth="1" style="17" min="16" max="16"/>
-    <col width="21.28515625" bestFit="1" customWidth="1" style="17" min="17" max="17"/>
-    <col width="15.7109375" bestFit="1" customWidth="1" style="19" min="18" max="19"/>
-    <col width="16.7109375" bestFit="1" customWidth="1" style="19" min="20" max="20"/>
-    <col width="19.5703125" bestFit="1" customWidth="1" style="19" min="21" max="21"/>
-    <col width="15.7109375" bestFit="1" customWidth="1" style="16" min="22" max="22"/>
-    <col width="25.85546875" customWidth="1" style="14" min="23" max="23"/>
-    <col width="32.140625" customWidth="1" style="14" min="24" max="24"/>
-    <col width="31.140625" customWidth="1" style="14" min="25" max="25"/>
-    <col width="17.7109375" customWidth="1" style="19" min="30" max="30"/>
-    <col width="15.140625" customWidth="1" style="19" min="31" max="31"/>
-    <col width="26.28515625" customWidth="1" style="19" min="32" max="32"/>
-    <col width="22.28515625" customWidth="1" style="19" min="33" max="33"/>
+    <col min="1" max="1" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="15.7109375" style="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.28515625" style="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.5703125" customWidth="1"/>
+    <col min="6" max="6" width="25.85546875" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="15.7109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="21.28515625" style="16" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="15.7109375" style="18" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.7109375" style="18" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="19.5703125" style="18" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.7109375" style="15" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="25.85546875" customWidth="1"/>
+    <col min="24" max="24" width="32.140625" customWidth="1"/>
+    <col min="25" max="25" width="31.140625" customWidth="1"/>
+    <col min="30" max="30" width="17.7109375" style="18" customWidth="1"/>
+    <col min="31" max="31" width="15.140625" style="18" customWidth="1"/>
+    <col min="32" max="32" width="26.28515625" style="18" customWidth="1"/>
+    <col min="33" max="33" width="22.28515625" style="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.5" customHeight="1" s="14" thickBot="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Tipo Dato</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
-      </c>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Periodo Desde</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>Periodo Hasta</t>
-        </is>
-      </c>
-      <c r="E1" s="5" t="inlineStr">
-        <is>
-          <t>Condicion frente al IVA</t>
-        </is>
-      </c>
-      <c r="F1" s="5" t="inlineStr">
-        <is>
-          <t>Tipo Doc</t>
-        </is>
-      </c>
-      <c r="G1" s="6" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
-      <c r="H1" s="7" t="inlineStr">
-        <is>
-          <t>Documento</t>
-        </is>
-      </c>
-      <c r="I1" s="5" t="inlineStr">
-        <is>
-          <t>Domicilio</t>
-        </is>
-      </c>
-      <c r="J1" s="8" t="inlineStr">
-        <is>
-          <t>Cant.</t>
-        </is>
-      </c>
-      <c r="K1" s="6" t="inlineStr">
-        <is>
-          <t>Descripcion</t>
-        </is>
-      </c>
-      <c r="L1" s="9" t="inlineStr">
-        <is>
-          <t>$ Unit.</t>
-        </is>
-      </c>
-      <c r="M1" s="10" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="N1" s="11" t="inlineStr">
-        <is>
-          <t>Condición Venta</t>
-        </is>
-      </c>
-      <c r="O1" s="11" t="inlineStr">
-        <is>
-          <t>Unidad Medida</t>
-        </is>
-      </c>
-      <c r="P1" s="12" t="inlineStr">
-        <is>
-          <t>% Bonificación</t>
-        </is>
-      </c>
-      <c r="Q1" s="12" t="inlineStr">
-        <is>
-          <t>Importe Bonificación</t>
-        </is>
-      </c>
-      <c r="R1" s="13" t="inlineStr">
-        <is>
-          <t>Importe Op Ex</t>
-        </is>
-      </c>
-      <c r="S1" s="13" t="inlineStr">
-        <is>
-          <t>Importe IVA</t>
-        </is>
-      </c>
-      <c r="T1" s="13" t="inlineStr">
-        <is>
-          <t>Importe Tributos</t>
-        </is>
-      </c>
-      <c r="U1" s="13" t="inlineStr">
-        <is>
-          <t>Observaciones</t>
-        </is>
-      </c>
-      <c r="V1" s="10" t="inlineStr">
-        <is>
-          <t>Concepto</t>
-        </is>
-      </c>
-      <c r="W1" s="10" t="inlineStr">
-        <is>
-          <t>Codigo Otros Tributos</t>
-        </is>
-      </c>
-      <c r="X1" s="10" t="inlineStr">
-        <is>
-          <t>Descripión Otros Tributos</t>
-        </is>
-      </c>
-      <c r="Y1" s="10" t="inlineStr">
-        <is>
-          <t>Base Imponible Otros Tributos</t>
-        </is>
-      </c>
-      <c r="AD1" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Comprobación</t>
-        </is>
-      </c>
-      <c r="AE1" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> CAE</t>
-        </is>
-      </c>
-      <c r="AF1" s="18" t="inlineStr">
-        <is>
-          <t>Fecha Vencimiento CAE</t>
-        </is>
-      </c>
-      <c r="AG1" s="18" t="inlineStr">
-        <is>
-          <t>Número Comprobante</t>
-        </is>
+    <row r="1" spans="1:34" s="29" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="V1" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="X1" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y1" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z1" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD1" s="30"/>
+      <c r="AE1" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF1" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG1" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH1" s="17" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="14">
-      <c r="W14" s="29" t="n"/>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="W14" s="28"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:M1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="22.140625" customWidth="1" style="19" min="1" max="1"/>
-    <col width="34.85546875" customWidth="1" style="28" min="2" max="2"/>
-    <col width="22.85546875" customWidth="1" style="15" min="3" max="3"/>
-    <col width="22.85546875" customWidth="1" style="19" min="4" max="4"/>
-    <col width="22.85546875" customWidth="1" style="19" min="5" max="5"/>
-    <col width="26" customWidth="1" style="16" min="6" max="6"/>
-    <col width="25.85546875" customWidth="1" style="19" min="7" max="7"/>
-    <col width="30.140625" customWidth="1" style="16" min="8" max="8"/>
-    <col width="24.140625" customWidth="1" style="16" min="9" max="9"/>
-    <col width="38" customWidth="1" style="19" min="10" max="10"/>
+    <col min="1" max="1" width="22.140625" style="18" customWidth="1"/>
+    <col min="2" max="2" width="34.85546875" style="27" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" style="14" customWidth="1"/>
+    <col min="4" max="5" width="22.85546875" style="18" customWidth="1"/>
+    <col min="6" max="6" width="26" style="15" customWidth="1"/>
+    <col min="7" max="7" width="25.85546875" style="18" customWidth="1"/>
+    <col min="8" max="8" width="30.140625" style="15" customWidth="1"/>
+    <col min="9" max="9" width="24.140625" style="15" customWidth="1"/>
+    <col min="10" max="10" width="38" style="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" s="14" thickBot="1">
-      <c r="A1" s="26" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="B1" s="27" t="inlineStr">
-        <is>
-          <t>Número Comprobante Original</t>
-        </is>
-      </c>
-      <c r="C1" s="20" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
-      </c>
-      <c r="D1" s="20" t="inlineStr">
-        <is>
-          <t>Periodo Desde</t>
-        </is>
-      </c>
-      <c r="E1" s="20" t="inlineStr">
-        <is>
-          <t>Periodo Hasta</t>
-        </is>
-      </c>
-      <c r="F1" s="20" t="inlineStr">
-        <is>
-          <t>Fecha vencimiento pago</t>
-        </is>
-      </c>
-      <c r="G1" s="21" t="inlineStr">
-        <is>
-          <t>Tipo Doc</t>
-        </is>
-      </c>
-      <c r="H1" s="22" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
-      <c r="I1" s="23" t="inlineStr">
-        <is>
-          <t>Documento</t>
-        </is>
-      </c>
-      <c r="J1" s="21" t="inlineStr">
-        <is>
-          <t>Domicilio</t>
-        </is>
-      </c>
-      <c r="K1" s="24" t="inlineStr">
-        <is>
-          <t>Importe Total</t>
-        </is>
-      </c>
-      <c r="L1" s="24" t="inlineStr">
-        <is>
-          <t>Concepto</t>
-        </is>
-      </c>
-      <c r="M1" s="25" t="inlineStr">
-        <is>
-          <t>Motivo Nota</t>
-        </is>
+    <row r="1" spans="1:13" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1" s="24" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -970,92 +939,61 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="22.140625" customWidth="1" style="19" min="1" max="1"/>
-    <col width="34.85546875" customWidth="1" style="28" min="2" max="2"/>
-    <col width="22.85546875" customWidth="1" style="15" min="3" max="3"/>
-    <col width="22.85546875" customWidth="1" style="19" min="4" max="4"/>
-    <col width="22.85546875" customWidth="1" style="19" min="5" max="5"/>
-    <col width="26" customWidth="1" style="16" min="6" max="6"/>
-    <col width="25.85546875" customWidth="1" style="19" min="7" max="7"/>
-    <col width="30.140625" customWidth="1" style="16" min="8" max="8"/>
-    <col width="24.140625" customWidth="1" style="16" min="9" max="9"/>
-    <col width="38" customWidth="1" style="19" min="10" max="10"/>
-    <col width="11.42578125" customWidth="1" style="14" min="11" max="16384"/>
+    <col min="1" max="1" width="22.140625" style="18" customWidth="1"/>
+    <col min="2" max="2" width="34.85546875" style="27" customWidth="1"/>
+    <col min="3" max="3" width="22.85546875" style="14" customWidth="1"/>
+    <col min="4" max="5" width="22.85546875" style="18" customWidth="1"/>
+    <col min="6" max="6" width="26" style="15" customWidth="1"/>
+    <col min="7" max="7" width="25.85546875" style="18" customWidth="1"/>
+    <col min="8" max="8" width="30.140625" style="15" customWidth="1"/>
+    <col min="9" max="9" width="24.140625" style="15" customWidth="1"/>
+    <col min="10" max="10" width="38" style="18" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="14" thickBot="1">
-      <c r="A1" s="26" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="B1" s="27" t="inlineStr">
-        <is>
-          <t>Número Comprobante Original</t>
-        </is>
-      </c>
-      <c r="C1" s="20" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
-      </c>
-      <c r="D1" s="20" t="inlineStr">
-        <is>
-          <t>Periodo Desde</t>
-        </is>
-      </c>
-      <c r="E1" s="20" t="inlineStr">
-        <is>
-          <t>Periodo Hasta</t>
-        </is>
-      </c>
-      <c r="F1" s="20" t="inlineStr">
-        <is>
-          <t>Fecha vencimiento pago</t>
-        </is>
-      </c>
-      <c r="G1" s="21" t="inlineStr">
-        <is>
-          <t>Tipo Doc</t>
-        </is>
-      </c>
-      <c r="H1" s="22" t="inlineStr">
-        <is>
-          <t>Cliente</t>
-        </is>
-      </c>
-      <c r="I1" s="23" t="inlineStr">
-        <is>
-          <t>Documento</t>
-        </is>
-      </c>
-      <c r="J1" s="21" t="inlineStr">
-        <is>
-          <t>Domicilio</t>
-        </is>
-      </c>
-      <c r="K1" s="24" t="inlineStr">
-        <is>
-          <t>Importe Total</t>
-        </is>
-      </c>
-      <c r="L1" s="24" t="inlineStr">
-        <is>
-          <t>Concepto</t>
-        </is>
-      </c>
-      <c r="M1" s="25" t="inlineStr">
-        <is>
-          <t>Motivo Nota</t>
-        </is>
+    <row r="1" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="22" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1" s="24" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
